--- a/entregables/plan-de-validacion.xlsx
+++ b/entregables/plan-de-validacion.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="340">
   <si>
     <t xml:space="preserve">Plan de validación — Chatbot de WhatsApp (A) y Sorpresas y detalles (B)</t>
   </si>
@@ -665,6 +665,27 @@
   </si>
   <si>
     <t xml:space="preserve">Una que frecuenta Carlos (A1-6) y una que frecuenta Indira (A1-7). Ir como clientes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AJUSTE 2026-10-22 — Meta (verificado en fuentes oficiales)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A0: dónde entrar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">developers.facebook.com → App Dashboard → tu app → WhatsApp → API Setup. Ahí Meta asigna un número de prueba sin verificación ni tarjeta. NO entrar por Business Suite / WhatsApp Manager: ahí aparece el flujo de verificación con documentos. Si aun así pide documentos: captura de pantalla y demo simulada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A2: pregunta adicional (S-47)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"La cuenta de WhatsApp Business y el número quedan a nombre de su negocio; usted registra su tarjeta en Meta solo para el excedente sobre los 1 000 mensajes gratuitos al mes. ¿Está de acuerdo?" → anotar sí/no.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A3: cómo se instala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuenta y número a nombre del cliente (chip nuevo, no registrado antes en WhatsApp); Carlos con rol en su cuenta y en la app. Sin verificar el negocio: un bot que solo responde dentro de la ventana de 24 h no toca el límite de 250. Verificación con RUC: Etapa 2.</t>
   </si>
   <si>
     <t xml:space="preserve">Registro de resultados — llenen las celdas amarillas. Las celdas 'Criterio' se calculan solas.</t>
@@ -1183,16 +1204,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1200,7 +1225,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1240,43 +1265,51 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1535,100 +1568,100 @@
   <dimension ref="A1:B14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="95"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
+    <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="4" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1651,333 +1684,333 @@
   <dimension ref="A1:N10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="12" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="12" style="1" width="10"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
+    <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="M2" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="N2" s="6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="7" t="n">
+      <c r="B3" s="8" t="n">
         <v>46322</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="8" t="n">
         <v>46327</v>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="7" t="n">
         <f aca="false">SUMIFS('A Chatbot'!G$3:G$21,'A Chatbot'!$D$3:$D$21,"&gt;="&amp;$B3,'A Chatbot'!$D$3:$D$21,"&lt;="&amp;$C3)</f>
         <v>6</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="E3" s="7" t="n">
         <f aca="false">SUMIFS('B Detalles'!G$3:G$15,'B Detalles'!$D$3:$D$15,"&gt;="&amp;$B3,'B Detalles'!$D$3:$D$15,"&lt;="&amp;$C3)</f>
         <v>1</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="F3" s="7" t="n">
         <f aca="false">D3+E3</f>
         <v>7</v>
       </c>
-      <c r="G3" s="6" t="str">
+      <c r="G3" s="7" t="str">
         <f aca="false">IF(F3&lt;=10,"Sí","NO: recortar")</f>
         <v>Sí</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="H3" s="7" t="n">
         <f aca="false">SUMIFS('A Chatbot'!H$3:H$21,'A Chatbot'!$D$3:$D$21,"&gt;="&amp;$B3,'A Chatbot'!$D$3:$D$21,"&lt;="&amp;$C3)</f>
         <v>2</v>
       </c>
-      <c r="I3" s="6" t="n">
+      <c r="I3" s="7" t="n">
         <f aca="false">SUMIFS('B Detalles'!H$3:H$15,'B Detalles'!$D$3:$D$15,"&gt;="&amp;$B3,'B Detalles'!$D$3:$D$15,"&lt;="&amp;$C3)</f>
         <v>4</v>
       </c>
-      <c r="J3" s="6" t="n">
+      <c r="J3" s="7" t="n">
         <f aca="false">H3+I3</f>
         <v>6</v>
       </c>
-      <c r="K3" s="6" t="str">
+      <c r="K3" s="7" t="str">
         <f aca="false">IF(J3&lt;=10,"Sí","NO: recortar")</f>
         <v>Sí</v>
       </c>
-      <c r="L3" s="6" t="n">
+      <c r="L3" s="7" t="n">
         <f aca="false">SUMIFS('A Chatbot'!I$3:I$21,'A Chatbot'!$D$3:$D$21,"&gt;="&amp;$B3,'A Chatbot'!$D$3:$D$21,"&lt;="&amp;$C3)</f>
         <v>0</v>
       </c>
-      <c r="M3" s="6" t="n">
+      <c r="M3" s="7" t="n">
         <f aca="false">SUMIFS('B Detalles'!I$3:I$15,'B Detalles'!$D$3:$D$15,"&gt;="&amp;$B3,'B Detalles'!$D$3:$D$15,"&lt;="&amp;$C3)</f>
         <v>50</v>
       </c>
-      <c r="N3" s="6" t="n">
+      <c r="N3" s="7" t="n">
         <f aca="false">L3+M3</f>
         <v>50</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="7" t="n">
+      <c r="B4" s="8" t="n">
         <v>46328</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="8" t="n">
         <v>46334</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="7" t="n">
         <f aca="false">SUMIFS('A Chatbot'!G$3:G$21,'A Chatbot'!$D$3:$D$21,"&gt;="&amp;$B4,'A Chatbot'!$D$3:$D$21,"&lt;="&amp;$C4)</f>
         <v>8.5</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" s="7" t="n">
         <f aca="false">SUMIFS('B Detalles'!G$3:G$15,'B Detalles'!$D$3:$D$15,"&gt;="&amp;$B4,'B Detalles'!$D$3:$D$15,"&lt;="&amp;$C4)</f>
         <v>0.5</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F4" s="7" t="n">
         <f aca="false">D4+E4</f>
         <v>9</v>
       </c>
-      <c r="G4" s="6" t="str">
+      <c r="G4" s="7" t="str">
         <f aca="false">IF(F4&lt;=10,"Sí","NO: recortar")</f>
         <v>Sí</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="H4" s="7" t="n">
         <f aca="false">SUMIFS('A Chatbot'!H$3:H$21,'A Chatbot'!$D$3:$D$21,"&gt;="&amp;$B4,'A Chatbot'!$D$3:$D$21,"&lt;="&amp;$C4)</f>
         <v>4</v>
       </c>
-      <c r="I4" s="6" t="n">
+      <c r="I4" s="7" t="n">
         <f aca="false">SUMIFS('B Detalles'!H$3:H$15,'B Detalles'!$D$3:$D$15,"&gt;="&amp;$B4,'B Detalles'!$D$3:$D$15,"&lt;="&amp;$C4)</f>
         <v>3.5</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="J4" s="7" t="n">
         <f aca="false">H4+I4</f>
         <v>7.5</v>
       </c>
-      <c r="K4" s="6" t="str">
+      <c r="K4" s="7" t="str">
         <f aca="false">IF(J4&lt;=10,"Sí","NO: recortar")</f>
         <v>Sí</v>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="L4" s="7" t="n">
         <f aca="false">SUMIFS('A Chatbot'!I$3:I$21,'A Chatbot'!$D$3:$D$21,"&gt;="&amp;$B4,'A Chatbot'!$D$3:$D$21,"&lt;="&amp;$C4)</f>
         <v>30</v>
       </c>
-      <c r="M4" s="6" t="n">
+      <c r="M4" s="7" t="n">
         <f aca="false">SUMIFS('B Detalles'!I$3:I$15,'B Detalles'!$D$3:$D$15,"&gt;="&amp;$B4,'B Detalles'!$D$3:$D$15,"&lt;="&amp;$C4)</f>
         <v>0</v>
       </c>
-      <c r="N4" s="6" t="n">
+      <c r="N4" s="7" t="n">
         <f aca="false">L4+M4</f>
         <v>30</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="7" t="n">
+      <c r="B5" s="8" t="n">
         <v>46335</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="8" t="n">
         <v>46341</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="7" t="n">
         <f aca="false">SUMIFS('A Chatbot'!G$3:G$21,'A Chatbot'!$D$3:$D$21,"&gt;="&amp;$B5,'A Chatbot'!$D$3:$D$21,"&lt;="&amp;$C5)</f>
         <v>3</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E5" s="7" t="n">
         <f aca="false">SUMIFS('B Detalles'!G$3:G$15,'B Detalles'!$D$3:$D$15,"&gt;="&amp;$B5,'B Detalles'!$D$3:$D$15,"&lt;="&amp;$C5)</f>
         <v>1</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="7" t="n">
         <f aca="false">D5+E5</f>
         <v>4</v>
       </c>
-      <c r="G5" s="6" t="str">
+      <c r="G5" s="7" t="str">
         <f aca="false">IF(F5&lt;=10,"Sí","NO: recortar")</f>
         <v>Sí</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="H5" s="7" t="n">
         <f aca="false">SUMIFS('A Chatbot'!H$3:H$21,'A Chatbot'!$D$3:$D$21,"&gt;="&amp;$B5,'A Chatbot'!$D$3:$D$21,"&lt;="&amp;$C5)</f>
         <v>3</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="I5" s="7" t="n">
         <f aca="false">SUMIFS('B Detalles'!H$3:H$15,'B Detalles'!$D$3:$D$15,"&gt;="&amp;$B5,'B Detalles'!$D$3:$D$15,"&lt;="&amp;$C5)</f>
         <v>5</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="J5" s="7" t="n">
         <f aca="false">H5+I5</f>
         <v>8</v>
       </c>
-      <c r="K5" s="6" t="str">
+      <c r="K5" s="7" t="str">
         <f aca="false">IF(J5&lt;=10,"Sí","NO: recortar")</f>
         <v>Sí</v>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="L5" s="7" t="n">
         <f aca="false">SUMIFS('A Chatbot'!I$3:I$21,'A Chatbot'!$D$3:$D$21,"&gt;="&amp;$B5,'A Chatbot'!$D$3:$D$21,"&lt;="&amp;$C5)</f>
         <v>0</v>
       </c>
-      <c r="M5" s="6" t="n">
+      <c r="M5" s="7" t="n">
         <f aca="false">SUMIFS('B Detalles'!I$3:I$15,'B Detalles'!$D$3:$D$15,"&gt;="&amp;$B5,'B Detalles'!$D$3:$D$15,"&lt;="&amp;$C5)</f>
         <v>35</v>
       </c>
-      <c r="N5" s="6" t="n">
+      <c r="N5" s="7" t="n">
         <f aca="false">L5+M5</f>
         <v>35</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B6" s="8" t="n">
         <v>46342</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="8" t="n">
         <v>46348</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="7" t="n">
         <f aca="false">SUMIFS('A Chatbot'!G$3:G$21,'A Chatbot'!$D$3:$D$21,"&gt;="&amp;$B6,'A Chatbot'!$D$3:$D$21,"&lt;="&amp;$C6)</f>
         <v>8</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="7" t="n">
         <f aca="false">SUMIFS('B Detalles'!G$3:G$15,'B Detalles'!$D$3:$D$15,"&gt;="&amp;$B6,'B Detalles'!$D$3:$D$15,"&lt;="&amp;$C6)</f>
         <v>2</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="7" t="n">
         <f aca="false">D6+E6</f>
         <v>10</v>
       </c>
-      <c r="G6" s="6" t="str">
+      <c r="G6" s="7" t="str">
         <f aca="false">IF(F6&lt;=10,"Sí","NO: recortar")</f>
         <v>Sí</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="H6" s="7" t="n">
         <f aca="false">SUMIFS('A Chatbot'!H$3:H$21,'A Chatbot'!$D$3:$D$21,"&gt;="&amp;$B6,'A Chatbot'!$D$3:$D$21,"&lt;="&amp;$C6)</f>
         <v>1</v>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="I6" s="7" t="n">
         <f aca="false">SUMIFS('B Detalles'!H$3:H$15,'B Detalles'!$D$3:$D$15,"&gt;="&amp;$B6,'B Detalles'!$D$3:$D$15,"&lt;="&amp;$C6)</f>
         <v>8</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="J6" s="7" t="n">
         <f aca="false">H6+I6</f>
         <v>9</v>
       </c>
-      <c r="K6" s="6" t="str">
+      <c r="K6" s="7" t="str">
         <f aca="false">IF(J6&lt;=10,"Sí","NO: recortar")</f>
         <v>Sí</v>
       </c>
-      <c r="L6" s="6" t="n">
+      <c r="L6" s="7" t="n">
         <f aca="false">SUMIFS('A Chatbot'!I$3:I$21,'A Chatbot'!$D$3:$D$21,"&gt;="&amp;$B6,'A Chatbot'!$D$3:$D$21,"&lt;="&amp;$C6)</f>
         <v>15</v>
       </c>
-      <c r="M6" s="6" t="n">
+      <c r="M6" s="7" t="n">
         <f aca="false">SUMIFS('B Detalles'!I$3:I$15,'B Detalles'!$D$3:$D$15,"&gt;="&amp;$B6,'B Detalles'!$D$3:$D$15,"&lt;="&amp;$C6)</f>
         <v>0</v>
       </c>
-      <c r="N6" s="6" t="n">
+      <c r="N6" s="7" t="n">
         <f aca="false">L6+M6</f>
         <v>15</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="3" t="n">
         <f aca="false">SUM(D3:D6)</f>
         <v>25.5</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="3" t="n">
         <f aca="false">SUM(E3:E6)</f>
         <v>4.5</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="3" t="n">
         <f aca="false">SUM(F3:F6)</f>
         <v>30</v>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="H7" s="3" t="n">
         <f aca="false">SUM(H3:H6)</f>
         <v>10</v>
       </c>
-      <c r="I7" s="2" t="n">
+      <c r="I7" s="3" t="n">
         <f aca="false">SUM(I3:I6)</f>
         <v>20.5</v>
       </c>
-      <c r="J7" s="2" t="n">
+      <c r="J7" s="3" t="n">
         <f aca="false">SUM(J3:J6)</f>
         <v>30.5</v>
       </c>
-      <c r="L7" s="2" t="n">
+      <c r="L7" s="3" t="n">
         <f aca="false">SUM(L3:L6)</f>
         <v>45</v>
       </c>
-      <c r="M7" s="2" t="n">
+      <c r="M7" s="3" t="n">
         <f aca="false">SUM(M3:M6)</f>
         <v>85</v>
       </c>
-      <c r="N7" s="2" t="n">
+      <c r="N7" s="3" t="n">
         <f aca="false">SUM(N3:N6)</f>
         <v>130</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
         <v>44</v>
       </c>
     </row>
@@ -2000,899 +2033,899 @@
   <dimension ref="A1:P22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="60"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="40"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
+    <row r="2" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="M2" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="N2" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="O2" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="P2" s="6" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="D3" s="9" t="n">
+      <c r="D3" s="10" t="n">
         <v>46322</v>
       </c>
-      <c r="E3" s="9" t="n">
+      <c r="E3" s="10" t="n">
         <v>46322</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="G3" s="8" t="n">
+      <c r="G3" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="8" t="s">
+      <c r="H3" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="L3" s="10" t="s">
+      <c r="L3" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="M3" s="10"/>
-      <c r="N3" s="10"/>
-      <c r="O3" s="10"/>
-      <c r="P3" s="10"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
+      <c r="O3" s="11"/>
+      <c r="P3" s="11"/>
     </row>
     <row r="4" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D4" s="10" t="n">
         <v>46323</v>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="E4" s="10" t="n">
         <v>46323</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="G4" s="8" t="n">
+      <c r="G4" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="H4" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="8" t="s">
+      <c r="H4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="K4" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="L4" s="10" t="s">
+      <c r="L4" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="M4" s="10"/>
-      <c r="N4" s="10"/>
-      <c r="O4" s="10"/>
-      <c r="P4" s="10"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="11"/>
+      <c r="O4" s="11"/>
+      <c r="P4" s="11"/>
     </row>
     <row r="5" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="10" t="n">
         <v>46324</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="10" t="n">
         <v>46324</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="G5" s="8" t="n">
+      <c r="G5" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="H5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="8" t="s">
+      <c r="H5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="K5" s="8" t="s">
+      <c r="K5" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="L5" s="10" t="s">
+      <c r="L5" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
-      <c r="O5" s="10"/>
-      <c r="P5" s="10"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11"/>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
     </row>
     <row r="6" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="10" t="n">
         <v>46323</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="10" t="n">
         <v>46323</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="G6" s="8" t="n">
+      <c r="G6" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="8" t="n">
+      <c r="H6" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="8" t="s">
+      <c r="I6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="K6" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="L6" s="10" t="s">
+      <c r="L6" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
-      <c r="O6" s="10"/>
-      <c r="P6" s="10"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="11"/>
+      <c r="O6" s="11"/>
+      <c r="P6" s="11"/>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="10" t="n">
         <v>46324</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="10" t="n">
         <v>46327</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="G7" s="8" t="n">
+      <c r="G7" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="H7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="8" t="s">
+      <c r="H7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="K7" s="8" t="s">
+      <c r="K7" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="L7" s="10" t="s">
+      <c r="L7" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="10"/>
-      <c r="P7" s="10"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="11"/>
+      <c r="P7" s="11"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D8" s="10" t="n">
         <v>46324</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E8" s="10" t="n">
         <v>46327</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="G8" s="8" t="n">
+      <c r="G8" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="H8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="8" t="s">
+      <c r="H8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="K8" s="8" t="s">
+      <c r="K8" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="L8" s="10" t="s">
+      <c r="L8" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="M8" s="10"/>
-      <c r="N8" s="10"/>
-      <c r="O8" s="10"/>
-      <c r="P8" s="10"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="11"/>
+      <c r="O8" s="11"/>
+      <c r="P8" s="11"/>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="D9" s="9" t="n">
+      <c r="D9" s="10" t="n">
         <v>46325</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="10" t="n">
         <v>46330</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="G9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="8" t="n">
+      <c r="G9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="8" t="s">
+      <c r="I9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="K9" s="8" t="s">
+      <c r="K9" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="L9" s="10" t="s">
+      <c r="L9" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="10"/>
-      <c r="P9" s="10"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="11"/>
+      <c r="P9" s="11"/>
     </row>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="10" t="n">
         <v>46328</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="10" t="n">
         <v>46331</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="G10" s="8" t="n">
+      <c r="G10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="8" t="s">
+      <c r="H10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="K10" s="8" t="s">
+      <c r="K10" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="L10" s="10" t="s">
+      <c r="L10" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
-      <c r="O10" s="10"/>
-      <c r="P10" s="10"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="11"/>
+      <c r="O10" s="11"/>
+      <c r="P10" s="11"/>
     </row>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="D11" s="9" t="n">
+      <c r="D11" s="10" t="n">
         <v>46329</v>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="E11" s="10" t="n">
         <v>46333</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="G11" s="8" t="n">
+      <c r="G11" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="H11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="8" t="n">
+      <c r="H11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="J11" s="8" t="s">
+      <c r="J11" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="K11" s="8" t="s">
+      <c r="K11" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="L11" s="10" t="s">
+      <c r="L11" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="M11" s="10"/>
-      <c r="N11" s="10"/>
-      <c r="O11" s="10"/>
-      <c r="P11" s="10"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="11"/>
+      <c r="P11" s="11"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="D12" s="10" t="n">
         <v>46329</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="10" t="n">
         <v>46333</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="G12" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="8" t="n">
+      <c r="G12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="I12" s="8" t="n">
+      <c r="I12" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="J12" s="8" t="s">
+      <c r="J12" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="K12" s="8" t="s">
+      <c r="K12" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="L12" s="10" t="s">
+      <c r="L12" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="M12" s="10"/>
-      <c r="N12" s="10"/>
-      <c r="O12" s="10"/>
-      <c r="P12" s="10"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="11"/>
+      <c r="O12" s="11"/>
+      <c r="P12" s="11"/>
     </row>
     <row r="13" customFormat="false" ht="105" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="D13" s="10" t="n">
         <v>46334</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="E13" s="10" t="n">
         <v>46334</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="G13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="8" t="n">
+      <c r="G13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="8" t="s">
+      <c r="I13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="K13" s="8" t="s">
+      <c r="K13" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="L13" s="10" t="s">
+      <c r="L13" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
-      <c r="O13" s="10"/>
-      <c r="P13" s="10"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="11"/>
+      <c r="P13" s="11"/>
     </row>
     <row r="14" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="D14" s="9" t="n">
+      <c r="D14" s="10" t="n">
         <v>46330</v>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="E14" s="10" t="n">
         <v>46330</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="G14" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="8" t="n">
+      <c r="G14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="I14" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="8" t="s">
+      <c r="I14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="K14" s="8" t="s">
+      <c r="K14" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="L14" s="10" t="s">
+      <c r="L14" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="M14" s="10"/>
-      <c r="N14" s="10"/>
-      <c r="O14" s="10"/>
-      <c r="P14" s="10"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="11"/>
+      <c r="O14" s="11"/>
+      <c r="P14" s="11"/>
     </row>
     <row r="15" customFormat="false" ht="105" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="D15" s="9" t="n">
+      <c r="D15" s="10" t="n">
         <v>46329</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E15" s="10" t="n">
         <v>46334</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F15" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="G15" s="8" t="n">
+      <c r="G15" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="H15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="8" t="s">
+      <c r="H15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="K15" s="8" t="s">
+      <c r="K15" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="L15" s="10" t="s">
+      <c r="L15" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="M15" s="10"/>
-      <c r="N15" s="10"/>
-      <c r="O15" s="10"/>
-      <c r="P15" s="10"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="11"/>
+      <c r="P15" s="11"/>
     </row>
     <row r="16" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="D16" s="9" t="n">
+      <c r="D16" s="10" t="n">
         <v>46335</v>
       </c>
-      <c r="E16" s="9" t="n">
+      <c r="E16" s="10" t="n">
         <v>46340</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F16" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="G16" s="8" t="n">
+      <c r="G16" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="H16" s="8" t="n">
+      <c r="H16" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I16" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="8" t="s">
+      <c r="I16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="K16" s="8" t="s">
+      <c r="K16" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="L16" s="10" t="s">
+      <c r="L16" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="M16" s="10"/>
-      <c r="N16" s="10"/>
-      <c r="O16" s="10"/>
-      <c r="P16" s="10"/>
+      <c r="M16" s="11"/>
+      <c r="N16" s="11"/>
+      <c r="O16" s="11"/>
+      <c r="P16" s="11"/>
     </row>
     <row r="17" customFormat="false" ht="105" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="D17" s="9" t="n">
+      <c r="D17" s="10" t="n">
         <v>46335</v>
       </c>
-      <c r="E17" s="9" t="n">
+      <c r="E17" s="10" t="n">
         <v>46341</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="F17" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="G17" s="8" t="n">
+      <c r="G17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H17" s="8" t="n">
+      <c r="H17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I17" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="8" t="s">
+      <c r="I17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="K17" s="8" t="s">
+      <c r="K17" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="L17" s="10" t="s">
+      <c r="L17" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="M17" s="10"/>
-      <c r="N17" s="10"/>
-      <c r="O17" s="10"/>
-      <c r="P17" s="10"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="11"/>
+      <c r="O17" s="11"/>
+      <c r="P17" s="11"/>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="D18" s="9" t="n">
+      <c r="D18" s="10" t="n">
         <v>46342</v>
       </c>
-      <c r="E18" s="9" t="n">
+      <c r="E18" s="10" t="n">
         <v>46343</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="F18" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="G18" s="8" t="n">
+      <c r="G18" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="H18" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="8" t="n">
+      <c r="H18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="J18" s="8" t="s">
+      <c r="J18" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="K18" s="8" t="s">
+      <c r="K18" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="L18" s="10" t="s">
+      <c r="L18" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="M18" s="10"/>
-      <c r="N18" s="10"/>
-      <c r="O18" s="10"/>
-      <c r="P18" s="10"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="11"/>
+      <c r="O18" s="11"/>
+      <c r="P18" s="11"/>
     </row>
     <row r="19" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="D19" s="9" t="n">
+      <c r="D19" s="10" t="n">
         <v>46342</v>
       </c>
-      <c r="E19" s="9" t="n">
+      <c r="E19" s="10" t="n">
         <v>46346</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="F19" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="G19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="8" t="n">
+      <c r="G19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="8" t="s">
+      <c r="I19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="K19" s="8" t="s">
+      <c r="K19" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="L19" s="10" t="s">
+      <c r="L19" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="M19" s="10"/>
-      <c r="N19" s="10"/>
-      <c r="O19" s="10"/>
-      <c r="P19" s="10"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="11"/>
+      <c r="P19" s="11"/>
     </row>
     <row r="20" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="D20" s="9" t="n">
+      <c r="D20" s="10" t="n">
         <v>46342</v>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="E20" s="10" t="n">
         <v>46362</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="F20" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="G20" s="8" t="n">
+      <c r="G20" s="9" t="n">
         <v>6.5</v>
       </c>
-      <c r="H20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="8" t="s">
+      <c r="H20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="K20" s="8" t="s">
+      <c r="K20" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="L20" s="10" t="s">
+      <c r="L20" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="M20" s="10"/>
-      <c r="N20" s="10"/>
-      <c r="O20" s="10"/>
-      <c r="P20" s="10"/>
+      <c r="M20" s="11"/>
+      <c r="N20" s="11"/>
+      <c r="O20" s="11"/>
+      <c r="P20" s="11"/>
     </row>
     <row r="21" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="D21" s="9" t="n">
+      <c r="D21" s="10" t="n">
         <v>46346</v>
       </c>
-      <c r="E21" s="9" t="n">
+      <c r="E21" s="10" t="n">
         <v>46346</v>
       </c>
-      <c r="F21" s="8" t="s">
+      <c r="F21" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="G21" s="8" t="n">
+      <c r="G21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="8" t="s">
+      <c r="H21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="K21" s="8" t="s">
+      <c r="K21" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="L21" s="10" t="s">
+      <c r="L21" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="M21" s="10"/>
-      <c r="N21" s="10"/>
-      <c r="O21" s="10"/>
-      <c r="P21" s="10"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C22" s="2" t="s">
+      <c r="M21" s="11"/>
+      <c r="N21" s="11"/>
+      <c r="O21" s="11"/>
+      <c r="P21" s="11"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C22" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="G22" s="2" t="n">
+      <c r="G22" s="3" t="n">
         <f aca="false">SUM(G3:G21)</f>
         <v>25.5</v>
       </c>
-      <c r="H22" s="2" t="n">
+      <c r="H22" s="3" t="n">
         <f aca="false">SUM(H3:H21)</f>
         <v>10</v>
       </c>
-      <c r="I22" s="2" t="n">
+      <c r="I22" s="3" t="n">
         <f aca="false">SUM(I3:I21)</f>
         <v>45</v>
       </c>
-      <c r="M22" s="2" t="n">
+      <c r="M22" s="3" t="n">
         <f aca="false">SUM(M3:M21)</f>
         <v>0</v>
       </c>
-      <c r="N22" s="2" t="n">
+      <c r="N22" s="3" t="n">
         <f aca="false">SUM(N3:N21)</f>
         <v>0</v>
       </c>
-      <c r="O22" s="2" t="n">
+      <c r="O22" s="3" t="n">
         <f aca="false">SUM(O3:O21)</f>
         <v>0</v>
       </c>
@@ -2922,647 +2955,647 @@
   <dimension ref="A1:P16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="60"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="40"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
+    <row r="2" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="M2" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="N2" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="O2" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="P2" s="6" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="D3" s="12" t="n">
+      <c r="D3" s="13" t="n">
         <v>46323</v>
       </c>
-      <c r="E3" s="12" t="n">
+      <c r="E3" s="13" t="n">
         <v>46323</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="G3" s="11" t="n">
+      <c r="G3" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="11" t="s">
+      <c r="H3" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="L3" s="10" t="s">
+      <c r="L3" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="M3" s="10"/>
-      <c r="N3" s="10"/>
-      <c r="O3" s="10"/>
-      <c r="P3" s="10"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
+      <c r="O3" s="11"/>
+      <c r="P3" s="11"/>
     </row>
     <row r="4" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="D4" s="12" t="n">
+      <c r="D4" s="13" t="n">
         <v>46325</v>
       </c>
-      <c r="E4" s="12" t="n">
+      <c r="E4" s="13" t="n">
         <v>46325</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="G4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="11" t="s">
+      <c r="G4" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="L4" s="10" t="s">
+      <c r="L4" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="M4" s="10"/>
-      <c r="N4" s="10"/>
-      <c r="O4" s="10"/>
-      <c r="P4" s="10"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="11"/>
+      <c r="O4" s="11"/>
+      <c r="P4" s="11"/>
     </row>
     <row r="5" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="D5" s="12" t="n">
+      <c r="D5" s="13" t="n">
         <v>46326</v>
       </c>
-      <c r="E5" s="12" t="n">
+      <c r="E5" s="13" t="n">
         <v>46326</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="G5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="11" t="n">
+      <c r="G5" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I5" s="11" t="n">
+      <c r="I5" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="J5" s="11" t="s">
+      <c r="J5" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="K5" s="11" t="s">
+      <c r="K5" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="L5" s="10" t="s">
+      <c r="L5" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
-      <c r="O5" s="10"/>
-      <c r="P5" s="10"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11"/>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="D6" s="13" t="n">
         <v>46326</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="13" t="n">
         <v>46326</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="G6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="11" t="n">
+      <c r="G6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="12" t="n">
         <v>1.5</v>
       </c>
-      <c r="I6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="11" t="s">
+      <c r="I6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="K6" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="L6" s="10" t="s">
+      <c r="L6" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
-      <c r="O6" s="10"/>
-      <c r="P6" s="10"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="11"/>
+      <c r="O6" s="11"/>
+      <c r="P6" s="11"/>
     </row>
     <row r="7" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="D7" s="13" t="n">
         <v>46327</v>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="E7" s="13" t="n">
         <v>46327</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="G7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="11" t="n">
+      <c r="G7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="I7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="11" t="s">
+      <c r="I7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="K7" s="11" t="s">
+      <c r="K7" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="L7" s="10" t="s">
+      <c r="L7" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="10"/>
-      <c r="P7" s="10"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="11"/>
+      <c r="P7" s="11"/>
     </row>
     <row r="8" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="D8" s="13" t="n">
         <v>46328</v>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="E8" s="13" t="n">
         <v>46328</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="G8" s="11" t="n">
+      <c r="G8" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="H8" s="11" t="n">
+      <c r="H8" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="11" t="s">
+      <c r="I8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="K8" s="11" t="s">
+      <c r="K8" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="L8" s="10" t="s">
+      <c r="L8" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="M8" s="10"/>
-      <c r="N8" s="10"/>
-      <c r="O8" s="10"/>
-      <c r="P8" s="10"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="11"/>
+      <c r="O8" s="11"/>
+      <c r="P8" s="11"/>
     </row>
     <row r="9" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="D9" s="13" t="n">
         <v>46328</v>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="E9" s="13" t="n">
         <v>46334</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="G9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="11" t="n">
+      <c r="G9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="12" t="n">
         <v>2.5</v>
       </c>
-      <c r="I9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="11" t="s">
+      <c r="I9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="K9" s="11" t="s">
+      <c r="K9" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="L9" s="10" t="s">
+      <c r="L9" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="10"/>
-      <c r="P9" s="10"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="11"/>
+      <c r="P9" s="11"/>
     </row>
     <row r="10" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="D10" s="12" t="n">
+      <c r="D10" s="13" t="n">
         <v>46335</v>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="E10" s="13" t="n">
         <v>46341</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="G10" s="11" t="n">
+      <c r="G10" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="H10" s="11" t="n">
+      <c r="H10" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="11" t="s">
+      <c r="I10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="K10" s="11" t="s">
+      <c r="K10" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="L10" s="10" t="s">
+      <c r="L10" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
-      <c r="O10" s="10"/>
-      <c r="P10" s="10"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="11"/>
+      <c r="O10" s="11"/>
+      <c r="P10" s="11"/>
     </row>
     <row r="11" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="D11" s="13" t="n">
         <v>46337</v>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="E11" s="13" t="n">
         <v>46337</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="G11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="11" t="n">
+      <c r="G11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="11" t="n">
+      <c r="I11" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="J11" s="11" t="s">
+      <c r="J11" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="K11" s="11" t="s">
+      <c r="K11" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="L11" s="10" t="s">
+      <c r="L11" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="M11" s="10"/>
-      <c r="N11" s="10"/>
-      <c r="O11" s="10"/>
-      <c r="P11" s="10"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="11"/>
+      <c r="P11" s="11"/>
     </row>
     <row r="12" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="D12" s="12" t="n">
+      <c r="D12" s="13" t="n">
         <v>46338</v>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="E12" s="13" t="n">
         <v>46341</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="G12" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="H12" s="11" t="n">
+      <c r="H12" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="11" t="s">
+      <c r="I12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="K12" s="11" t="s">
+      <c r="K12" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="L12" s="10" t="s">
+      <c r="L12" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="M12" s="10"/>
-      <c r="N12" s="10"/>
-      <c r="O12" s="10"/>
-      <c r="P12" s="10"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="11"/>
+      <c r="O12" s="11"/>
+      <c r="P12" s="11"/>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="D13" s="12" t="n">
+      <c r="D13" s="13" t="n">
         <v>46342</v>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="E13" s="13" t="n">
         <v>46344</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="G13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="11" t="n">
+      <c r="G13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="11" t="s">
+      <c r="I13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="K13" s="11" t="s">
+      <c r="K13" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="L13" s="10" t="s">
+      <c r="L13" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
-      <c r="O13" s="10"/>
-      <c r="P13" s="10"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="11"/>
+      <c r="P13" s="11"/>
     </row>
     <row r="14" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="D14" s="12" t="n">
+      <c r="D14" s="13" t="n">
         <v>46347</v>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="E14" s="13" t="n">
         <v>46355</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="G14" s="11" t="n">
+      <c r="G14" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H14" s="11" t="n">
+      <c r="H14" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I14" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="11" t="s">
+      <c r="I14" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="K14" s="11" t="s">
+      <c r="K14" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="L14" s="10" t="s">
+      <c r="L14" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="M14" s="10"/>
-      <c r="N14" s="10"/>
-      <c r="O14" s="10"/>
-      <c r="P14" s="10"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="11"/>
+      <c r="O14" s="11"/>
+      <c r="P14" s="11"/>
     </row>
     <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="D15" s="12" t="n">
+      <c r="D15" s="13" t="n">
         <v>46346</v>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="E15" s="13" t="n">
         <v>46346</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="F15" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="G15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="11" t="n">
+      <c r="G15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="11" t="s">
+      <c r="I15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="K15" s="11" t="s">
+      <c r="K15" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="L15" s="10" t="s">
+      <c r="L15" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="M15" s="10"/>
-      <c r="N15" s="10"/>
-      <c r="O15" s="10"/>
-      <c r="P15" s="10"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C16" s="2" t="s">
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="11"/>
+      <c r="P15" s="11"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C16" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="G16" s="2" t="n">
+      <c r="G16" s="3" t="n">
         <f aca="false">SUM(G3:G15)</f>
         <v>4.5</v>
       </c>
-      <c r="H16" s="2" t="n">
+      <c r="H16" s="3" t="n">
         <f aca="false">SUM(H3:H15)</f>
         <v>20.5</v>
       </c>
-      <c r="I16" s="2" t="n">
+      <c r="I16" s="3" t="n">
         <f aca="false">SUM(I3:I15)</f>
         <v>85</v>
       </c>
-      <c r="M16" s="2" t="n">
+      <c r="M16" s="3" t="n">
         <f aca="false">SUM(M3:M15)</f>
         <v>0</v>
       </c>
-      <c r="N16" s="2" t="n">
+      <c r="N16" s="3" t="n">
         <f aca="false">SUM(N3:N15)</f>
         <v>0</v>
       </c>
-      <c r="O16" s="2" t="n">
+      <c r="O16" s="3" t="n">
         <f aca="false">SUM(O3:O15)</f>
         <v>0</v>
       </c>
@@ -3589,163 +3622,192 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="110"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="110"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="B1" s="3"/>
+      <c r="B1" s="4"/>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="4" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="4" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13" t="s">
+      <c r="A16" s="14" t="s">
         <v>202</v>
       </c>
-      <c r="B16" s="3"/>
+      <c r="B16" s="4"/>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="4" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="4" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="4" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="4" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="4" t="s">
         <v>212</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="15" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="16" t="s">
+        <v>216</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="16" t="s">
+        <v>218</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -3767,854 +3829,854 @@
   <dimension ref="A1:K88"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="F4" s="5" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="G4" s="5" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="H4" s="5" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="14" t="s">
+      <c r="E4" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="17" t="s">
         <v>203</v>
       </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
-        <v>226</v>
-      </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14" t="s">
+      <c r="B5" s="18"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="18"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="17" t="s">
+        <v>233</v>
+      </c>
+      <c r="B6" s="18"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="17" t="s">
         <v>207</v>
       </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14" t="s">
+      <c r="B7" s="18"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="18"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="17" t="s">
         <v>209</v>
       </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14" t="s">
-        <v>227</v>
-      </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="14" t="s">
-        <v>228</v>
-      </c>
-      <c r="B10" s="15"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="B11" s="2" t="n">
+      <c r="B8" s="18"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="18"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="17" t="s">
+        <v>234</v>
+      </c>
+      <c r="B9" s="18"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="18"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="B10" s="18"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="18"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="B11" s="3" t="n">
         <f aca="false">COUNTA(F5:F10)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="B12" s="2" t="n">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="B12" s="3" t="n">
         <f aca="false">COUNTIF(F5:F10,"&gt;=80")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="B13" s="2" t="n">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="B13" s="3" t="n">
         <f aca="false">COUNTIF(G5:G10,"Sí")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="B14" s="2" t="n">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="B14" s="3" t="n">
         <f aca="false">COUNTIF(F5:F10,"&gt;0")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="B15" s="2" t="n">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="B15" s="3" t="n">
         <f aca="false">COUNTIF(D5:D10,"&lt;231")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="B16" s="2" t="n">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="B16" s="3" t="n">
         <f aca="false">COUNTIF(I5:I10,"&gt;=100")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="B17" s="17" t="str">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B17" s="20" t="str">
         <f aca="false">IF(B11&lt;5,"Faltan entrevistas (mínimo 5)",IF(AND(B12&gt;=3,B13&gt;=1),"PASA → hacer A2",IF(B14=2,"REPETIR CON CAMBIO → A2 con módulo básico a S/ 50 → S/ 80","NO PASA → A2 no se hace; chatbot a banda 31-ene")))</f>
         <v>Faltan entrevistas (mínimo 5)</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="B18" s="2" t="str">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="B18" s="3" t="str">
         <f aca="false">IF(B11&lt;5,"Pendiente",IF(B16&gt;=2,"Sigue vivo en reserva","Se archiva"))</f>
         <v>Pendiente</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B19" s="2" t="str">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="B19" s="3" t="str">
         <f aca="false">IF(B11&lt;5,"Pendiente",IF(B15&gt;=4,"Se mantiene S/ 33,07","Recalcular S-29 con el volumen real"))</f>
         <v>Pendiente</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="G22" s="5" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="H22" s="5" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="15"/>
-      <c r="B23" s="15"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="15"/>
-      <c r="B24" s="15"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="15"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="15"/>
-      <c r="B25" s="15"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="15"/>
-      <c r="B26" s="15"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="15"/>
-      <c r="B27" s="15"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="15"/>
-      <c r="B28" s="15"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="s">
+    </row>
+    <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="B29" s="2" t="n">
+      <c r="B22" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="18"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="18"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="18"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="18"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="18"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="18"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="B29" s="3" t="n">
         <f aca="false">COUNTIF(D23:D28,"&gt;0")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="B30" s="2" t="n">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="B30" s="3" t="n">
         <f aca="false">SUM(D23:D28)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="B31" s="2" t="n">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="B31" s="3" t="n">
         <f aca="false">COUNTIF(B23:B28,"Sí cuando lo vea funcionando")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="B32" s="2" t="n">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="B32" s="3" t="n">
         <f aca="false">COUNTIF(F23:F28,"Sí")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="B33" s="17" t="str">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="B33" s="20" t="str">
         <f aca="false">IF(COUNTA(B23:B28)=0,"Pendiente",IF(B29&gt;=2,"PASA (escenario base) → A3",IF(B29=1,"PASA (escenario pesimista) → A3",IF(B31&gt;=2,"REPETIR CON CAMBIO → ofrecer 14 días gratis a UNO, plazo 22-nov","NO PASA → no se construye nada"))))</f>
         <v>Pendiente</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="18" t="s">
-        <v>252</v>
-      </c>
-      <c r="B36" s="18" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="21" t="s">
+        <v>259</v>
+      </c>
+      <c r="B36" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="C36" s="18" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="B37" s="15"/>
-      <c r="C37" s="15"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="B38" s="15"/>
-      <c r="C38" s="15"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="B39" s="15"/>
-      <c r="C39" s="15"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="B40" s="15"/>
-      <c r="C40" s="15"/>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="B41" s="15"/>
-      <c r="C41" s="15"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="B42" s="15"/>
-      <c r="C42" s="15"/>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="4" t="s">
+      <c r="C36" s="21" t="s">
         <v>260</v>
       </c>
-      <c r="B43" s="15"/>
-      <c r="C43" s="15"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="4" t="s">
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="B44" s="15"/>
-      <c r="C44" s="15"/>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="4" t="s">
+      <c r="B37" s="18"/>
+      <c r="C37" s="18"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="B45" s="15"/>
-      <c r="C45" s="15"/>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="4" t="s">
+      <c r="B38" s="18"/>
+      <c r="C38" s="18"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="B46" s="15"/>
-      <c r="C46" s="15"/>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="2" t="s">
+      <c r="B39" s="18"/>
+      <c r="C39" s="18"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="B47" s="2" t="n">
+      <c r="B40" s="18"/>
+      <c r="C40" s="18"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="B41" s="18"/>
+      <c r="C41" s="18"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="B42" s="18"/>
+      <c r="C42" s="18"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="B43" s="18"/>
+      <c r="C43" s="18"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="B44" s="18"/>
+      <c r="C44" s="18"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="B45" s="18"/>
+      <c r="C45" s="18"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="B46" s="18"/>
+      <c r="C46" s="18"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B47" s="3" t="n">
         <f aca="false">SUM(B37:B46)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="B48" s="2" t="n">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B48" s="3" t="n">
         <f aca="false">B46</f>
         <v>0</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="B49" s="19"/>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="B50" s="19"/>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="B52" s="15"/>
-      <c r="C52" s="15"/>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="B53" s="15"/>
-      <c r="C53" s="15"/>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="4" t="s">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="B54" s="15"/>
-      <c r="C54" s="15"/>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="4" t="s">
+      <c r="B49" s="22"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="B55" s="15"/>
-      <c r="C55" s="15"/>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4" t="s">
+      <c r="B50" s="22"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="B56" s="15"/>
-      <c r="C56" s="15"/>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="4" t="s">
+      <c r="B51" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="B57" s="2" t="n">
+      <c r="C51" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="B52" s="18"/>
+      <c r="C52" s="18"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="B53" s="18"/>
+      <c r="C53" s="18"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="B54" s="18"/>
+      <c r="C54" s="18"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="B55" s="18"/>
+      <c r="C55" s="18"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="B56" s="18"/>
+      <c r="C56" s="18"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="B57" s="3" t="n">
         <f aca="false">COUNTIFS(B52:B56,"&gt;=60",B52:B56,"&lt;=100")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="B58" s="17" t="str">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="B58" s="20" t="str">
         <f aca="false">IF(B47=0,"Pendiente",IF(AND(B47&lt;=40,B57&gt;=3,B50&lt;=60,B48&lt;=20),"PASA → preventa a S/ 80 / S/ 95",IF(AND(B47&gt;40,B47&lt;=50,B48&lt;=20),"REPETIR CON CAMBIO → preventa a S/ 95 / S/ 110 (verificar ≥ 3 competidores en ese rango)","NO PASA → B2 y B3 no se hacen; B se descarta")))</f>
         <v>Pendiente</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="2" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="E61" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="F61" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="G61" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="H61" s="5" t="s">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="I61" s="5" t="s">
+    </row>
+    <row r="61" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="B61" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="J61" s="5" t="s">
+      <c r="C61" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="K61" s="5" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="15"/>
-      <c r="B62" s="16"/>
-      <c r="C62" s="15"/>
-      <c r="D62" s="15"/>
-      <c r="E62" s="15"/>
-      <c r="F62" s="15"/>
-      <c r="G62" s="15"/>
-      <c r="H62" s="16"/>
-      <c r="I62" s="15"/>
-      <c r="J62" s="15"/>
-      <c r="K62" s="15"/>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="15"/>
-      <c r="B63" s="16"/>
-      <c r="C63" s="15"/>
-      <c r="D63" s="15"/>
-      <c r="E63" s="15"/>
-      <c r="F63" s="15"/>
-      <c r="G63" s="15"/>
-      <c r="H63" s="16"/>
-      <c r="I63" s="15"/>
-      <c r="J63" s="15"/>
-      <c r="K63" s="15"/>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="15"/>
-      <c r="B64" s="16"/>
-      <c r="C64" s="15"/>
-      <c r="D64" s="15"/>
-      <c r="E64" s="15"/>
-      <c r="F64" s="15"/>
-      <c r="G64" s="15"/>
-      <c r="H64" s="16"/>
-      <c r="I64" s="15"/>
-      <c r="J64" s="15"/>
-      <c r="K64" s="15"/>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="15"/>
-      <c r="B65" s="16"/>
-      <c r="C65" s="15"/>
-      <c r="D65" s="15"/>
-      <c r="E65" s="15"/>
-      <c r="F65" s="15"/>
-      <c r="G65" s="15"/>
-      <c r="H65" s="16"/>
-      <c r="I65" s="15"/>
-      <c r="J65" s="15"/>
-      <c r="K65" s="15"/>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="15"/>
-      <c r="B66" s="16"/>
-      <c r="C66" s="15"/>
-      <c r="D66" s="15"/>
-      <c r="E66" s="15"/>
-      <c r="F66" s="15"/>
-      <c r="G66" s="15"/>
-      <c r="H66" s="16"/>
-      <c r="I66" s="15"/>
-      <c r="J66" s="15"/>
-      <c r="K66" s="15"/>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="15"/>
-      <c r="B67" s="16"/>
-      <c r="C67" s="15"/>
-      <c r="D67" s="15"/>
-      <c r="E67" s="15"/>
-      <c r="F67" s="15"/>
-      <c r="G67" s="15"/>
-      <c r="H67" s="16"/>
-      <c r="I67" s="15"/>
-      <c r="J67" s="15"/>
-      <c r="K67" s="15"/>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="15"/>
-      <c r="B68" s="16"/>
-      <c r="C68" s="15"/>
-      <c r="D68" s="15"/>
-      <c r="E68" s="15"/>
-      <c r="F68" s="15"/>
-      <c r="G68" s="15"/>
-      <c r="H68" s="16"/>
-      <c r="I68" s="15"/>
-      <c r="J68" s="15"/>
-      <c r="K68" s="15"/>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="15"/>
-      <c r="B69" s="16"/>
-      <c r="C69" s="15"/>
-      <c r="D69" s="15"/>
-      <c r="E69" s="15"/>
-      <c r="F69" s="15"/>
-      <c r="G69" s="15"/>
-      <c r="H69" s="16"/>
-      <c r="I69" s="15"/>
-      <c r="J69" s="15"/>
-      <c r="K69" s="15"/>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="15"/>
-      <c r="B70" s="16"/>
-      <c r="C70" s="15"/>
-      <c r="D70" s="15"/>
-      <c r="E70" s="15"/>
-      <c r="F70" s="15"/>
-      <c r="G70" s="15"/>
-      <c r="H70" s="16"/>
-      <c r="I70" s="15"/>
-      <c r="J70" s="15"/>
-      <c r="K70" s="15"/>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="15"/>
-      <c r="B71" s="16"/>
-      <c r="C71" s="15"/>
-      <c r="D71" s="15"/>
-      <c r="E71" s="15"/>
-      <c r="F71" s="15"/>
-      <c r="G71" s="15"/>
-      <c r="H71" s="16"/>
-      <c r="I71" s="15"/>
-      <c r="J71" s="15"/>
-      <c r="K71" s="15"/>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="15"/>
-      <c r="B72" s="16"/>
-      <c r="C72" s="15"/>
-      <c r="D72" s="15"/>
-      <c r="E72" s="15"/>
-      <c r="F72" s="15"/>
-      <c r="G72" s="15"/>
-      <c r="H72" s="16"/>
-      <c r="I72" s="15"/>
-      <c r="J72" s="15"/>
-      <c r="K72" s="15"/>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="15"/>
-      <c r="B73" s="16"/>
-      <c r="C73" s="15"/>
-      <c r="D73" s="15"/>
-      <c r="E73" s="15"/>
-      <c r="F73" s="15"/>
-      <c r="G73" s="15"/>
-      <c r="H73" s="16"/>
-      <c r="I73" s="15"/>
-      <c r="J73" s="15"/>
-      <c r="K73" s="15"/>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="4" t="s">
+      <c r="D61" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="B74" s="2" t="n">
+      <c r="E61" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="G61" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="H61" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="I61" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="J61" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="K61" s="6" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="18"/>
+      <c r="B62" s="19"/>
+      <c r="C62" s="18"/>
+      <c r="D62" s="18"/>
+      <c r="E62" s="18"/>
+      <c r="F62" s="18"/>
+      <c r="G62" s="18"/>
+      <c r="H62" s="19"/>
+      <c r="I62" s="18"/>
+      <c r="J62" s="18"/>
+      <c r="K62" s="18"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="18"/>
+      <c r="B63" s="19"/>
+      <c r="C63" s="18"/>
+      <c r="D63" s="18"/>
+      <c r="E63" s="18"/>
+      <c r="F63" s="18"/>
+      <c r="G63" s="18"/>
+      <c r="H63" s="19"/>
+      <c r="I63" s="18"/>
+      <c r="J63" s="18"/>
+      <c r="K63" s="18"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="18"/>
+      <c r="B64" s="19"/>
+      <c r="C64" s="18"/>
+      <c r="D64" s="18"/>
+      <c r="E64" s="18"/>
+      <c r="F64" s="18"/>
+      <c r="G64" s="18"/>
+      <c r="H64" s="19"/>
+      <c r="I64" s="18"/>
+      <c r="J64" s="18"/>
+      <c r="K64" s="18"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="18"/>
+      <c r="B65" s="19"/>
+      <c r="C65" s="18"/>
+      <c r="D65" s="18"/>
+      <c r="E65" s="18"/>
+      <c r="F65" s="18"/>
+      <c r="G65" s="18"/>
+      <c r="H65" s="19"/>
+      <c r="I65" s="18"/>
+      <c r="J65" s="18"/>
+      <c r="K65" s="18"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="18"/>
+      <c r="B66" s="19"/>
+      <c r="C66" s="18"/>
+      <c r="D66" s="18"/>
+      <c r="E66" s="18"/>
+      <c r="F66" s="18"/>
+      <c r="G66" s="18"/>
+      <c r="H66" s="19"/>
+      <c r="I66" s="18"/>
+      <c r="J66" s="18"/>
+      <c r="K66" s="18"/>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="18"/>
+      <c r="B67" s="19"/>
+      <c r="C67" s="18"/>
+      <c r="D67" s="18"/>
+      <c r="E67" s="18"/>
+      <c r="F67" s="18"/>
+      <c r="G67" s="18"/>
+      <c r="H67" s="19"/>
+      <c r="I67" s="18"/>
+      <c r="J67" s="18"/>
+      <c r="K67" s="18"/>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="18"/>
+      <c r="B68" s="19"/>
+      <c r="C68" s="18"/>
+      <c r="D68" s="18"/>
+      <c r="E68" s="18"/>
+      <c r="F68" s="18"/>
+      <c r="G68" s="18"/>
+      <c r="H68" s="19"/>
+      <c r="I68" s="18"/>
+      <c r="J68" s="18"/>
+      <c r="K68" s="18"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="18"/>
+      <c r="B69" s="19"/>
+      <c r="C69" s="18"/>
+      <c r="D69" s="18"/>
+      <c r="E69" s="18"/>
+      <c r="F69" s="18"/>
+      <c r="G69" s="18"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="18"/>
+      <c r="J69" s="18"/>
+      <c r="K69" s="18"/>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="18"/>
+      <c r="B70" s="19"/>
+      <c r="C70" s="18"/>
+      <c r="D70" s="18"/>
+      <c r="E70" s="18"/>
+      <c r="F70" s="18"/>
+      <c r="G70" s="18"/>
+      <c r="H70" s="19"/>
+      <c r="I70" s="18"/>
+      <c r="J70" s="18"/>
+      <c r="K70" s="18"/>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="18"/>
+      <c r="B71" s="19"/>
+      <c r="C71" s="18"/>
+      <c r="D71" s="18"/>
+      <c r="E71" s="18"/>
+      <c r="F71" s="18"/>
+      <c r="G71" s="18"/>
+      <c r="H71" s="19"/>
+      <c r="I71" s="18"/>
+      <c r="J71" s="18"/>
+      <c r="K71" s="18"/>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="18"/>
+      <c r="B72" s="19"/>
+      <c r="C72" s="18"/>
+      <c r="D72" s="18"/>
+      <c r="E72" s="18"/>
+      <c r="F72" s="18"/>
+      <c r="G72" s="18"/>
+      <c r="H72" s="19"/>
+      <c r="I72" s="18"/>
+      <c r="J72" s="18"/>
+      <c r="K72" s="18"/>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="18"/>
+      <c r="B73" s="19"/>
+      <c r="C73" s="18"/>
+      <c r="D73" s="18"/>
+      <c r="E73" s="18"/>
+      <c r="F73" s="18"/>
+      <c r="G73" s="18"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="18"/>
+      <c r="J73" s="18"/>
+      <c r="K73" s="18"/>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="B74" s="3" t="n">
         <f aca="false">COUNTIF(E62:E73,"Sí")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="B75" s="2" t="n">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="B75" s="3" t="n">
         <f aca="false">SUMIF(E62:E73,"Sí",D62:D73)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="B76" s="2" t="n">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="B76" s="3" t="n">
         <f aca="false">COUNTIFS(E62:E73,"Sí",F62:F73,"Sí")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="B77" s="2" t="n">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="B77" s="3" t="n">
         <f aca="false">COUNTIFS(E62:E73,"Sí",G62:G73,"No")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="B78" s="2" t="n">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="B78" s="3" t="n">
         <f aca="false">SUMIF(E62:E73,"Sí",I62:I73)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="B79" s="2" t="n">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="B79" s="3" t="n">
         <f aca="false">IF(B74=0,0,B78/B74)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="B80" s="2" t="n">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="B80" s="3" t="n">
         <f aca="false">IF(B74=0,0,SUMIF(E62:E73,"Sí",J62:J73)/B74)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="B81" s="17" t="str">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="B81" s="20" t="str">
         <f aca="false">IF(B74=0,"Pendiente",IF(AND(B74&gt;=6,B76&gt;=2,B77/B74&gt;=0.6),"PASA → B4 y desempate",IF(B74&gt;=4,"REPETIR CON CAMBIO → extender al 22-nov con segunda foto y variante","NO PASA → B se descarta; lo cobrado se entrega igual")))</f>
         <v>Pendiente</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="2" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="B84" s="19"/>
-    </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="B85" s="19"/>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="B86" s="19"/>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="B87" s="2" t="n">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="3" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="B84" s="22"/>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="B85" s="22"/>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="B86" s="22"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="B87" s="3" t="n">
         <f aca="false">IF(B84=0,0,B85/B84)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="B88" s="17" t="str">
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="B88" s="20" t="str">
         <f aca="false">IF(B85=0,"Pendiente o no aplica",IF(AND(B84&gt;=5,B87&lt;=8,B86&gt;=1),"PASA → B puede crecer fuera del círculo","NO PASA → B queda como demanda solo de conocidos; crecimiento 0 % en Etapa 2"))</f>
         <v>Pendiente o no aplica</v>
       </c>
@@ -4652,287 +4714,287 @@
   <dimension ref="A1:C30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="B4" s="20"/>
-      <c r="C4" s="4"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="B5" s="20" t="n">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B4" s="23"/>
+      <c r="C4" s="5"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="B5" s="23" t="n">
         <f aca="false">'Registro de resultados'!B30</f>
         <v>0</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="4" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="B7" s="20" t="n">
+      <c r="C5" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="B6" s="18"/>
+      <c r="C6" s="5" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="B7" s="23" t="n">
         <f aca="false">'Registro de resultados'!B32</f>
         <v>0</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="B8" s="15" t="n">
+      <c r="C7" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="B8" s="18" t="n">
         <v>150</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="B9" s="20" t="n">
+      <c r="C8" s="5" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="B9" s="23" t="n">
         <v>33.07</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="B10" s="23" t="n">
+        <f aca="false">SUM('A Chatbot'!M3:N17)</f>
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="B10" s="20" t="n">
-        <f aca="false">SUM('A Chatbot'!M3:N17)</f>
-        <v>0</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="B11" s="18"/>
+      <c r="C11" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="4" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="B12" s="20" t="n">
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="B12" s="23" t="n">
         <f aca="false">2*B7*2</f>
         <v>0</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="B13" s="21" t="n">
+      <c r="C12" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="B13" s="24" t="n">
         <f aca="false">B5-B6+2*(B8-B9)*B7</f>
         <v>0</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="B14" s="20" t="n">
+      <c r="C13" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="B14" s="23" t="n">
         <f aca="false">B10+IF(B11="",30,B11)+B12</f>
         <v>30</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="B15" s="21" t="n">
+      <c r="C14" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="B15" s="24" t="n">
         <f aca="false">IF(B14=0,0,B13/B14)</f>
         <v>0</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4"/>
-      <c r="B16" s="20"/>
-      <c r="C16" s="4"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="B17" s="20"/>
-      <c r="C17" s="4"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="B18" s="20" t="n">
+      <c r="C15" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5"/>
+      <c r="B16" s="23"/>
+      <c r="C16" s="5"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="B17" s="23"/>
+      <c r="C17" s="5"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="B18" s="23" t="n">
         <f aca="false">'Registro de resultados'!B75</f>
         <v>0</v>
       </c>
-      <c r="C18" s="4" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="B19" s="20" t="n">
+      <c r="C18" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="B19" s="23" t="n">
         <f aca="false">'Registro de resultados'!B78</f>
         <v>0</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="B20" s="20" t="n">
+      <c r="C19" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="B20" s="23" t="n">
         <f aca="false">SUM('B Detalles'!M3:N14)</f>
         <v>0</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="B21" s="21" t="n">
+      <c r="C20" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="B21" s="24" t="n">
         <f aca="false">B18-B19</f>
         <v>0</v>
       </c>
-      <c r="C21" s="4" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="B22" s="21" t="n">
+      <c r="C21" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="B22" s="24" t="n">
         <f aca="false">IF(B20=0,0,B21/B20)</f>
         <v>0</v>
       </c>
-      <c r="C22" s="4" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4"/>
-      <c r="B23" s="20"/>
-      <c r="C23" s="4"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="B24" s="20"/>
-      <c r="C24" s="4"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="B25" s="20" t="str">
+      <c r="C22" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5"/>
+      <c r="B23" s="23"/>
+      <c r="C23" s="5"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="B24" s="23"/>
+      <c r="C24" s="5"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="B25" s="23" t="str">
         <f aca="false">'Registro de resultados'!B33</f>
         <v>Pendiente</v>
       </c>
-      <c r="C25" s="4" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="B26" s="20" t="str">
+      <c r="C25" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="B26" s="23" t="str">
         <f aca="false">'Registro de resultados'!B81</f>
         <v>Pendiente</v>
       </c>
-      <c r="C26" s="4" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="B27" s="22" t="str">
+      <c r="C26" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="B27" s="25" t="str">
         <f aca="false">IF(OR(B25="Pendiente",B26="Pendiente"),"Pendiente: faltan resultados",IF(AND(LEFT(B25,4)="PASA",LEFT(B26,4)="PASA"),IF(ABS(B15-B22)&lt;0.2*MAX(B15,B22),"A (chatbot): diferencia &lt; 20 %, gana la recurrencia",IF(B15&gt;B22,"A (chatbot): mayor margen por hora","B (detalles): mayor margen por hora")),IF(LEFT(B25,4)="PASA","A (chatbot): la única que pasó",IF(LEFT(B26,4)="PASA","B (detalles): la única que pasó","Ninguna pasó → volver a Fase 3 (incógnito o taller)"))))</f>
         <v>Pendiente: faltan resultados</v>
       </c>
-      <c r="C27" s="4" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="B28" s="23" t="n">
+      <c r="C27" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="B28" s="26" t="n">
         <f aca="false">IF('Registro de resultados'!B75=0,0,SUMIFS('Registro de resultados'!D62:D73,'Registro de resultados'!E62:E73,"Sí",'Registro de resultados'!F62:F73,"Sí")/'Registro de resultados'!B75)</f>
         <v>0</v>
       </c>
-      <c r="C28" s="4" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="s">
-        <v>332</v>
+      <c r="C28" s="5" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5" t="s">
+        <v>339</v>
       </c>
     </row>
   </sheetData>
